--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,21 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-is-patient-new</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="769681006"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1098,9 +1112,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1457,12 +1468,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1852,7 +1857,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.43359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3732,7 +3737,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3747,11 +3752,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3784,30 +3791,30 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3830,13 +3837,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3887,7 +3894,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3911,7 +3918,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3922,10 +3929,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3954,7 +3961,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -3995,19 +4002,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4031,7 +4038,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4042,10 +4049,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4068,19 +4075,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4129,7 +4136,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4150,10 +4157,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4164,10 +4171,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4190,19 +4197,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4212,7 +4219,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4251,7 +4258,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4272,10 +4279,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4286,10 +4293,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4312,19 +4319,19 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4373,7 +4380,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4388,19 +4395,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4408,10 +4415,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4434,16 +4441,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4493,7 +4500,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4514,13 +4521,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4528,14 +4535,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4554,19 +4561,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4615,7 +4622,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4630,19 +4637,19 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4650,14 +4657,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4676,19 +4683,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4737,7 +4744,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4752,19 +4759,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4772,10 +4779,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4798,16 +4805,16 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4857,7 +4864,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4878,13 +4885,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4892,10 +4899,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4918,17 +4925,17 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4977,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4992,19 +4999,19 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5012,10 +5019,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5038,19 +5045,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5087,17 +5094,17 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5106,7 +5113,7 @@
         <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>104</v>
@@ -5115,30 +5122,30 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
@@ -5160,19 +5167,19 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5221,7 +5228,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5230,7 +5237,7 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
@@ -5239,27 +5246,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5285,16 +5292,16 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5319,13 +5326,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5343,7 +5350,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5352,7 +5359,7 @@
         <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>104</v>
@@ -5367,7 +5374,7 @@
         <v>135</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5378,14 +5385,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5407,16 +5414,16 @@
         <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5441,13 +5448,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5465,7 +5472,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5483,27 +5490,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5526,19 +5533,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5587,7 +5594,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5608,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5622,10 +5629,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5651,13 +5658,13 @@
         <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5683,13 +5690,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5707,7 +5714,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5725,27 +5732,27 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5771,16 +5778,16 @@
         <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5805,13 +5812,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5829,7 +5836,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5850,10 +5857,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5864,10 +5871,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5890,16 +5897,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5949,7 +5956,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5967,27 +5974,27 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6010,16 +6017,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6069,7 +6076,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6087,27 +6094,27 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6130,19 +6137,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6191,7 +6198,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6203,7 +6210,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6212,10 +6219,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6226,10 +6233,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6252,13 +6259,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6309,7 +6316,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6333,7 +6340,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6344,10 +6351,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6376,7 +6383,7 @@
         <v>139</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>141</v>
@@ -6429,7 +6436,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6453,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6464,14 +6471,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6493,10 +6500,10 @@
         <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>141</v>
@@ -6551,7 +6558,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6586,10 +6593,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6612,13 +6619,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6669,7 +6676,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6678,7 +6685,7 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
@@ -6690,10 +6697,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6704,10 +6711,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6730,13 +6737,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6787,7 +6794,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6796,7 +6803,7 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
@@ -6808,10 +6815,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6822,10 +6829,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6851,16 +6858,16 @@
         <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6888,10 +6895,10 @@
         <v>116</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6909,7 +6916,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6927,13 +6934,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6944,10 +6951,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6973,16 +6980,16 @@
         <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7007,13 +7014,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7031,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7049,13 +7056,13 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7066,10 +7073,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7092,17 +7099,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7151,7 +7158,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7175,7 +7182,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7186,10 +7193,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7212,13 +7219,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7269,7 +7276,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7290,10 +7297,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7304,10 +7311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7330,16 +7337,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7389,7 +7396,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7410,10 +7417,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7424,10 +7431,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7450,16 +7457,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7509,7 +7516,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7530,10 +7537,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7544,10 +7551,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7570,19 +7577,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7631,7 +7638,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7652,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7666,10 +7673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7692,13 +7699,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7749,7 +7756,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7773,7 +7780,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7784,10 +7791,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7816,7 +7823,7 @@
         <v>139</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>141</v>
@@ -7869,7 +7876,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7893,7 +7900,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7904,14 +7911,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7933,10 +7940,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>141</v>
@@ -7991,7 +7998,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8026,10 +8033,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8055,13 +8062,13 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>205</v>
@@ -8089,13 +8096,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>461</v>
+        <v>208</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>462</v>
+        <v>209</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8113,7 +8120,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>92</v>
@@ -8134,13 +8141,13 @@
         <v>463</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8180,13 +8187,13 @@
         <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>467</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8256,16 +8263,16 @@
         <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8308,7 +8315,7 @@
         <v>472</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8333,13 +8340,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8366,7 +8373,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8381,7 +8388,7 @@
         <v>135</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8399,7 +8406,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8421,16 +8428,16 @@
         <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8455,13 +8462,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8497,19 +8504,19 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8549,10 +8556,10 @@
         <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8622,10 +8629,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:44:23+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-05T21:01:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T21:01:51+00:00</t>
+    <t>2023-05-06T12:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:10:27+00:00</t>
+    <t>2023-05-06T12:11:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:11:33+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:06:01+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T12:57:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:57:45+00:00</t>
+    <t>2023-05-07T12:58:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:58:10+00:00</t>
+    <t>2023-05-07T13:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:06:46+00:00</t>
+    <t>2023-05-07T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:07:20+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-07T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:57:21+00:00</t>
+    <t>2023-05-08T06:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T06:55:26+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T13:44:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-09T07:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="480">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T07:17:44+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -474,7 +481,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -554,7 +561,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -590,7 +597,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -696,72 +703,72 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -789,7 +796,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -830,7 +837,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -888,7 +895,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -919,7 +926,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -972,7 +979,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1111,10 +1118,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1234,7 +1241,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1400,7 +1407,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1422,7 +1429,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1437,10 +1444,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1484,7 +1495,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2117,7 +2128,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2125,10 +2136,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2139,7 +2150,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2148,19 +2159,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2210,13 +2221,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2245,10 +2256,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2259,7 +2270,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2268,16 +2279,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2328,19 +2339,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2363,10 +2374,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2377,28 +2388,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2448,19 +2459,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2483,10 +2494,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2497,7 +2508,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2509,16 +2520,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2544,13 +2555,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2568,19 +2579,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2603,21 +2614,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2629,16 +2640,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2688,19 +2699,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2712,7 +2723,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2723,14 +2734,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2749,16 +2760,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2808,7 +2819,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2820,7 +2831,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2832,7 +2843,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2843,14 +2854,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2869,16 +2880,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2928,7 +2939,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2940,7 +2951,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2952,7 +2963,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2963,14 +2974,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2983,25 +2994,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3050,7 +3061,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3062,7 +3073,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3074,7 +3085,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3085,10 +3096,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3108,20 +3119,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3170,7 +3181,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3182,22 +3193,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3205,14 +3216,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3228,20 +3239,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3290,7 +3301,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3302,19 +3313,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3325,14 +3336,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3348,19 +3359,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3410,7 +3421,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3422,19 +3433,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3445,10 +3456,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3456,34 +3467,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3493,7 +3504,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3508,13 +3519,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3532,34 +3543,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3567,10 +3578,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3593,19 +3604,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3630,13 +3641,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3654,7 +3665,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3666,7 +3677,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3678,10 +3689,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3689,21 +3700,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3712,22 +3723,22 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3737,7 +3748,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3752,13 +3763,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3776,45 +3787,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3825,7 +3836,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3837,13 +3848,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3894,13 +3905,13 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
@@ -3918,7 +3929,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3929,14 +3940,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3955,16 +3966,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4002,19 +4013,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4026,7 +4037,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4038,7 +4049,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4049,10 +4060,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4072,22 +4083,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4136,7 +4147,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4148,7 +4159,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4157,10 +4168,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4171,10 +4182,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4185,7 +4196,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4194,22 +4205,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4219,7 +4230,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4258,19 +4269,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4279,10 +4290,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4293,10 +4304,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4304,10 +4315,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4316,22 +4327,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4380,34 +4391,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4415,10 +4426,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4438,19 +4449,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4500,7 +4511,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4512,7 +4523,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4521,13 +4532,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4535,21 +4546,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4558,22 +4569,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4622,34 +4633,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4657,21 +4668,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4680,22 +4691,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4744,34 +4755,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4779,10 +4790,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4793,7 +4804,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4802,19 +4813,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4864,19 +4875,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4885,13 +4896,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4899,10 +4910,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4922,20 +4933,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4984,7 +4995,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4996,22 +5007,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5019,10 +5030,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5030,10 +5041,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5042,22 +5053,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5094,68 +5105,68 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5164,22 +5175,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5228,45 +5239,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5277,7 +5288,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5289,19 +5300,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5326,13 +5337,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5350,19 +5361,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5371,10 +5382,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5385,14 +5396,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5411,19 +5422,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5448,13 +5459,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5472,7 +5483,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5484,33 +5495,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5524,7 +5535,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5533,19 +5544,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5594,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5606,7 +5617,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5615,10 +5626,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5629,10 +5640,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5643,7 +5654,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5655,16 +5666,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5690,13 +5701,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5714,45 +5725,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5763,7 +5774,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5775,19 +5786,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5812,13 +5823,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5836,19 +5847,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -5857,10 +5868,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5871,10 +5882,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5885,7 +5896,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5897,16 +5908,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5956,45 +5967,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6005,7 +6016,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6017,16 +6028,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6076,45 +6087,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6137,19 +6148,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6198,7 +6209,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6210,7 +6221,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6219,10 +6230,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6233,10 +6244,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6247,7 +6258,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6259,13 +6270,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6316,13 +6327,13 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
@@ -6340,7 +6351,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6351,14 +6362,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6377,16 +6388,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6436,7 +6447,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6448,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6460,7 +6471,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6471,14 +6482,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6491,25 +6502,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6558,7 +6569,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6570,7 +6581,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6582,7 +6593,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6593,10 +6604,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6607,7 +6618,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6619,13 +6630,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6676,19 +6687,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6697,10 +6708,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6711,10 +6722,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6725,7 +6736,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6737,13 +6748,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6794,31 +6805,31 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AG41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6829,10 +6840,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6843,7 +6854,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6855,19 +6866,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6892,13 +6903,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6916,31 +6927,31 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6951,10 +6962,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6977,19 +6988,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7014,13 +7025,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7038,7 +7049,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7050,19 +7061,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7073,10 +7084,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7087,7 +7098,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7099,17 +7110,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7158,19 +7169,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7182,7 +7193,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7193,10 +7204,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7207,7 +7218,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7219,13 +7230,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7276,19 +7287,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7297,10 +7308,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7311,10 +7322,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7334,19 +7345,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7396,7 +7407,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7408,7 +7419,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7417,10 +7428,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7431,10 +7442,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7454,19 +7465,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7516,7 +7527,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7528,7 +7539,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7537,10 +7548,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7551,10 +7562,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7574,22 +7585,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7638,7 +7649,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7650,7 +7661,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>456</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7659,10 +7670,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7673,10 +7684,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7687,7 +7698,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7699,13 +7710,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7756,13 +7767,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7780,7 +7791,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7791,14 +7802,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7817,16 +7828,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7876,7 +7887,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7888,7 +7899,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7900,7 +7911,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7911,14 +7922,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7931,25 +7942,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7998,7 +8009,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8010,7 +8021,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8022,7 +8033,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8033,10 +8044,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8044,10 +8055,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8056,22 +8067,22 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8096,13 +8107,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8120,34 +8131,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8155,10 +8166,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8169,7 +8180,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8178,22 +8189,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8242,45 +8253,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8291,7 +8302,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8303,19 +8314,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8340,13 +8351,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8364,19 +8375,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8385,10 +8396,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8399,14 +8410,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8425,19 +8436,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8462,13 +8473,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8486,7 +8497,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8498,33 +8509,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8550,16 +8561,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8608,7 +8619,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8631,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8629,10 +8640,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -481,7 +474,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -561,7 +554,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -597,7 +590,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -703,6 +696,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -765,10 +762,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -796,7 +789,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -837,7 +830,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -895,7 +888,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -926,7 +919,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -979,7 +972,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1118,10 +1111,10 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>SNOMED CT Body site concepts</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1241,7 +1234,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1407,7 +1400,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1429,7 +1422,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1444,14 +1437,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1495,7 +1484,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2128,7 +2117,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2136,10 +2125,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2150,28 +2139,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2221,13 +2210,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2256,10 +2245,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2270,25 +2259,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2339,19 +2328,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2374,10 +2363,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2388,28 +2377,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2459,19 +2448,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2494,10 +2483,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2508,7 +2497,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2520,16 +2509,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2555,43 +2544,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2614,21 +2603,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2640,16 +2629,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2699,31 +2688,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2734,14 +2723,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2760,16 +2749,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2819,7 +2808,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2831,7 +2820,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2843,7 +2832,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2854,14 +2843,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2880,16 +2869,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2939,7 +2928,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2951,7 +2940,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2963,7 +2952,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -2974,14 +2963,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2994,25 +2983,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3061,7 +3050,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3073,7 +3062,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3085,7 +3074,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3096,10 +3085,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3119,20 +3108,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3181,7 +3170,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3193,22 +3182,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3216,14 +3205,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3239,20 +3228,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3301,7 +3290,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3313,19 +3302,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3336,14 +3325,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3359,19 +3348,19 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3421,7 +3410,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3433,19 +3422,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3456,10 +3445,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3467,34 +3456,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="J14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3504,73 +3493,73 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AM14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3578,10 +3567,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3604,19 +3593,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3641,13 +3630,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3665,7 +3654,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3677,7 +3666,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3689,10 +3678,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3700,45 +3689,45 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3748,84 +3737,84 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="T16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AM16" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3836,7 +3825,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3848,13 +3837,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3905,31 +3894,31 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3940,14 +3929,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3966,16 +3955,16 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4013,19 +4002,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4037,7 +4026,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4049,7 +4038,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4060,10 +4049,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4083,22 +4072,22 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4147,7 +4136,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4159,7 +4148,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4168,10 +4157,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4182,10 +4171,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4196,31 +4185,31 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4230,70 +4219,70 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4304,10 +4293,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4315,34 +4304,34 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4391,34 +4380,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4426,10 +4415,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4449,19 +4438,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4511,7 +4500,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4523,7 +4512,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4532,13 +4521,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4546,45 +4535,45 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4633,34 +4622,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4668,45 +4657,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4755,34 +4744,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4790,10 +4779,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4804,28 +4793,28 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4875,19 +4864,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4896,13 +4885,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4910,10 +4899,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4933,20 +4922,20 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4995,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5007,22 +4996,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5030,10 +5019,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5041,34 +5030,34 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5105,92 +5094,92 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AF27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5239,45 +5228,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5288,7 +5277,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5300,19 +5289,19 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5337,55 +5326,55 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y29" t="s" s="2">
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z29" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5396,14 +5385,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5422,19 +5411,19 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5459,13 +5448,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5483,7 +5472,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5495,33 +5484,33 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5535,7 +5524,7 @@
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5544,19 +5533,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5605,7 +5594,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5617,7 +5606,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5626,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5640,10 +5629,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5654,7 +5643,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5666,16 +5655,16 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5701,69 +5690,69 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Z32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>357</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5774,7 +5763,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5786,19 +5775,19 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5823,55 +5812,55 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5882,10 +5871,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5896,7 +5885,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5908,16 +5897,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5967,45 +5956,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>375</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6016,7 +6005,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6028,16 +6017,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6087,45 +6076,45 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6148,19 +6137,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6209,7 +6198,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6221,19 +6210,19 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6244,10 +6233,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6258,7 +6247,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6270,13 +6259,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6327,31 +6316,31 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6362,14 +6351,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6388,16 +6377,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6447,7 +6436,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6459,7 +6448,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6471,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6482,14 +6471,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6502,25 +6491,25 @@
         <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6569,7 +6558,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6581,7 +6570,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6593,7 +6582,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6604,10 +6593,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6618,7 +6607,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6630,13 +6619,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6687,31 +6676,31 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6722,10 +6711,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6736,7 +6725,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6748,13 +6737,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6805,19 +6794,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6826,10 +6815,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6840,10 +6829,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6854,7 +6843,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6866,19 +6855,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6903,55 +6892,55 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6962,10 +6951,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6988,19 +6977,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7025,13 +7014,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7049,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7061,19 +7050,19 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7084,10 +7073,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7098,7 +7087,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7110,17 +7099,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7169,19 +7158,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7193,7 +7182,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7204,10 +7193,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7218,7 +7207,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7230,13 +7219,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7287,19 +7276,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7308,10 +7297,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7322,10 +7311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7345,19 +7334,19 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7407,7 +7396,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7419,7 +7408,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7428,10 +7417,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7442,10 +7431,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7465,19 +7454,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7527,7 +7516,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7539,7 +7528,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7548,10 +7537,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7562,10 +7551,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7585,22 +7574,22 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7649,7 +7638,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7661,7 +7650,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>456</v>
+        <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7670,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7684,10 +7673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7698,7 +7687,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7710,13 +7699,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7767,31 +7756,31 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7802,14 +7791,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7828,16 +7817,16 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7887,7 +7876,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7899,7 +7888,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7911,7 +7900,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7922,14 +7911,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7942,25 +7931,25 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8009,7 +7998,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8021,7 +8010,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8033,7 +8022,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8044,10 +8033,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8055,34 +8044,34 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G52" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8107,14 +8096,14 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8131,34 +8120,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8166,10 +8155,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8180,31 +8169,31 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8253,45 +8242,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>315</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8302,7 +8291,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8314,19 +8303,19 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8351,55 +8340,55 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z54" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="Y54" t="s" s="2">
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="Z54" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8410,14 +8399,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8436,19 +8425,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8473,13 +8462,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8497,7 +8486,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8509,33 +8498,33 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8561,16 +8550,16 @@
         <v>83</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8619,7 +8608,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8631,7 +8620,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8640,10 +8629,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:35:55+00:00</t>
+    <t>2023-05-10T08:50:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,16 +240,16 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
     <t>Mapping: SNOMED CT Concept Domain Binding</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
@@ -284,13 +284,16 @@
     <t>Event</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity|</t>
   </si>
   <si>
     <t>OBX</t>
   </si>
   <si>
-    <t>Observation[classCode=OBS, moodCode=EVN]</t>
+    <t>Entity, Role, or Act,Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -312,7 +315,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -351,7 +354,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -373,13 +376,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -402,10 +405,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -425,13 +432,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -451,7 +462,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -470,11 +481,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -499,13 +510,35 @@
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>OBX-21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 3) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
+    <t>Observation.instantiates[x]</t>
+  </si>
+  <si>
+    <t>canonical(ObservationDefinition)
+Reference(ObservationDefinition)</t>
+  </si>
+  <si>
+    <t>Instantiates FHIR ObservationDefinition</t>
+  </si>
+  <si>
+    <t>The reference to a FHIR ObservationDefinition resource that provides the definition that is adhered to in whole or in part by this Observation instance.</t>
+  </si>
+  <si>
+    <t>ObservationDefinition can be referenced by its canonical url using instantiatesCanonical, or by a name or an identifier using the appropriate sub-elements of instantiatesReference.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
   </si>
   <si>
     <t>Observation.basedOn</t>
@@ -537,6 +570,115 @@
     <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
   </si>
   <si>
+    <t>Observation.triggeredBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Triggering observation(s)</t>
+  </si>
+  <si>
+    <t>Identifies the observation(s) that triggered the performance of this observation.</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.observation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation)
+</t>
+  </si>
+  <si>
+    <t>Triggering observation</t>
+  </si>
+  <si>
+    <t>Reference to the triggering observation.</t>
+  </si>
+  <si>
+    <t>outBoundRelationship</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.type</t>
+  </si>
+  <si>
+    <t>reflex | repeat | re-run</t>
+  </si>
+  <si>
+    <t>The type of trigger.
+Reflex | Repeat | Re-run.</t>
+  </si>
+  <si>
+    <t>The type of TriggeredBy Observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-triggeredbytype|5.0.0</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>Observation.triggeredBy.reason</t>
+  </si>
+  <si>
+    <t>Reason that the observation was triggered</t>
+  </si>
+  <si>
+    <t>Provides the reason why this observation was performed as a result of the observation(s) referenced.</t>
+  </si>
+  <si>
+    <t>annotation</t>
+  </si>
+  <si>
     <t>Observation.partOf</t>
   </si>
   <si>
@@ -544,7 +686,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy|GenomicStudy)
 </t>
   </si>
   <si>
@@ -554,7 +696,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -584,18 +726,18 @@
     <t>final</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|5.0.0</t>
   </si>
   <si>
     <t>Event.status</t>
   </si>
   <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
     <t>&lt; 445584004 |Report by finality status|</t>
   </si>
   <si>
@@ -603,9 +745,6 @@
   </si>
   <si>
     <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -627,16 +766,19 @@
     <t>Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -675,47 +817,29 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
     <t>OBX-3</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -728,9 +852,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.code.coding</t>
   </si>
   <si>
@@ -789,17 +910,17 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance|BiologicallyDerivedProduct|NutritionProduct)
 </t>
   </si>
   <si>
     <t>Who and/or what the observation is about</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
   </si>
   <si>
     <t>Observations have no value if you don't know who or what they're about.</t>
@@ -808,13 +929,13 @@
     <t>Event.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>PID-3</t>
   </si>
   <si>
     <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -830,7 +951,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [http://hl7.org/fhir/StructureDefinition/observation-focusCode](http://hl7.org/fhir/extensions/StructureDefinition-observation-focusCode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -859,16 +980,16 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>Event.context</t>
+    <t>Event.encounter</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
   </si>
   <si>
     <t>PV1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -888,7 +1009,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R5/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -897,13 +1018,13 @@
     <t>Event.occurrence[x]</t>
   </si>
   <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
     <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
   </si>
   <si>
     <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -919,16 +1040,16 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+    <t>For Observations that don't require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R5/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn't require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>OBR-22 (or MSH-7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
     <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Observation.performer</t>
@@ -950,13 +1071,13 @@
     <t>Event.performer.actor</t>
   </si>
   <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>OBX-15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
   </si>
   <si>
     <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -972,7 +1093,15 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>- An observation may have:
+  1.  a single value here
+  1.  both a value and a set of related or component values
+  1.  only a set of related or component values.
+-  If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- The usage of valueReference is restricted to the MolecularSequence resource when used as a definitional resource, not as a patient-specific finding. .
+- For additional guidance, see the [Notes section](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -985,14 +1114,14 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">obs-7
-</t>
+    <t>obs-7
+obs-6</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
   </si>
   <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
+    <t>OBX-2, OBX-5, OBX-6</t>
   </si>
   <si>
     <t>value</t>
@@ -1046,7 +1175,7 @@
 </t>
   </si>
   <si>
-    <t>High, low, normal, etc.</t>
+    <t>High, low, normal, etc</t>
   </si>
   <si>
     <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
@@ -1095,7 +1224,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
+    <t>NTE-3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
@@ -1110,16 +1239,19 @@
     <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
   </si>
   <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.</t>
+  </si>
+  <si>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t xml:space="preserve">obs-8
+</t>
+  </si>
+  <si>
     <t>&lt; 123037004 |Body structure|</t>
   </si>
   <si>
@@ -1132,6 +1264,22 @@
     <t>718497002 |Inherent location|</t>
   </si>
   <si>
+    <t>Observation.bodyStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>Observed body structure</t>
+  </si>
+  <si>
+    <t>Indicates the body structure on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code or bodySite is used. In many systems, this may be represented as a related observation instead of an inline component.</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1162,7 +1310,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|Group)
 </t>
   </si>
   <si>
@@ -1173,6 +1321,10 @@
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-9:If Observation.specimen is a reference to Group, the group can only have specimens {(reference.resolve().exists() and reference.resolve() is Group) implies reference.resolve().member.entity.resolve().all($this is Specimen)}</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -1194,10 +1346,10 @@
 </t>
   </si>
   <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
+    <t>A reference to the device that generates the measurements or the device settings for the device</t>
+  </si>
+  <si>
+    <t>A reference to the device that generates the measurements or the device settings for the device.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -1216,10 +1368,6 @@
   </si>
   <si>
     <t>Observation.referenceRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
   </si>
   <si>
     <t>Provides guide for interpretation</t>
@@ -1238,7 +1386,7 @@
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
-    <t>OBX.7</t>
+    <t>OBX-7</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=REFV]/target[classCode=OBS, moodCode=EVN]</t>
@@ -1251,20 +1399,6 @@
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
     <t>Observation.referenceRange.low</t>
@@ -1284,9 +1418,6 @@
 </t>
   </si>
   <si>
-    <t>OBX-7</t>
-  </si>
-  <si>
     <t>value:IVL_PQ.low</t>
   </si>
   <si>
@@ -1300,6 +1431,24 @@
   </si>
   <si>
     <t>value:IVL_PQ.high</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.normalValue</t>
+  </si>
+  <si>
+    <t>Normal value, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the normal value of the reference range.</t>
+  </si>
+  <si>
+    <t>Codes identifying the normal value of the observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-referencerange-normalvalue</t>
+  </si>
+  <si>
+    <t>value:IVL_PQ.normal</t>
   </si>
   <si>
     <t>Observation.referenceRange.type</t>
@@ -1378,6 +1527,10 @@
     <t>Observation.referenceRange.text</t>
   </si>
   <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
     <t>Text based reference range in an observation</t>
   </si>
   <si>
@@ -1400,29 +1553,26 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R5/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
   </si>
   <si>
-    <t>outBoundRelationship</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|ImagingSelection|QuestionnaireResponse|Observation|MolecularSequence|GenomicStudy)
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
+    <t>Related resource from which the observation is made</t>
   </si>
   <si>
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R5/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1437,7 +1587,7 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
@@ -1478,13 +1628,22 @@
   </si>
   <si>
     <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriodAttachmentReference(MolecularSequence)</t>
   </si>
   <si>
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations:
+-  An observation may have both a value (e.g. an  Apgar score) and component observations (the observations from which the Apgar score was derived). 
+-  If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- If a value is present, the datatype for this element should be determined by the `code`.
+-  *CodeableConcept* with just a text would be used instead of a string if the field was usually coded, or if the type associated with the `code` defines a coded value.
+-  *Attachment* is used if the observation result value is a binary file such as an image.  If the observation result value is derived from the binary file (for example 'X' detected and here is the the proof in this image), the binary file may be directly represented using *DocumentReference* and referenced by `derivedFrom`.
+- The usage of valueReference is restricted to the MolecularSequence resource when used as a definitional resource, not as a patient-specific finding. .
+- For additional guidance, see the [Notes section](http://hl7.org/fhir/R5/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -1661,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1748,77 +1907,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1829,7 +1996,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP56"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -1842,7 +2009,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="111.11328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="135.15234375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1857,7 +2024,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.02734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1868,10 +2035,10 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2117,7 +2284,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2125,10 +2292,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2139,7 +2306,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2148,19 +2315,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2210,13 +2377,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2245,10 +2412,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2259,7 +2426,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2268,16 +2435,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2328,19 +2495,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2363,10 +2530,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2377,28 +2544,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2448,19 +2615,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2483,10 +2650,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2497,7 +2664,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2509,16 +2676,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2544,13 +2711,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2568,19 +2735,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2603,21 +2770,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2629,16 +2796,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2688,19 +2855,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2712,10 +2879,10 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
-        <v>82</v>
+        <v>129</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>82</v>
@@ -2723,14 +2890,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2749,16 +2916,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2808,7 +2975,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2817,7 +2984,7 @@
         <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>82</v>
@@ -2832,10 +2999,10 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>82</v>
@@ -2843,14 +3010,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2869,16 +3036,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2928,7 +3095,7 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2940,7 +3107,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2952,10 +3119,10 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -2963,14 +3130,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2983,25 +3150,25 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3050,7 +3217,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3062,7 +3229,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3074,10 +3241,10 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -3085,10 +3252,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3108,20 +3275,20 @@
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3170,7 +3337,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3182,22 +3349,22 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3205,21 +3372,21 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -3228,21 +3395,21 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3290,34 +3457,34 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3325,14 +3492,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3348,21 +3515,21 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N13" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="O13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -3410,7 +3577,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3422,22 +3589,22 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>175</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>82</v>
@@ -3445,10 +3612,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3456,35 +3623,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O14" t="s" s="2">
         <v>180</v>
       </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3493,7 +3656,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3508,13 +3671,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3532,34 +3695,34 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3567,10 +3730,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3581,7 +3744,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3593,20 +3756,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3630,13 +3789,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3654,19 +3813,19 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -3678,10 +3837,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3689,21 +3848,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>140</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3712,23 +3871,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3737,7 +3894,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3752,13 +3909,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3776,77 +3933,81 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3894,19 +4055,19 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -3918,10 +4079,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3929,21 +4090,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3952,20 +4113,18 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4002,31 +4161,31 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4038,10 +4197,10 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4049,10 +4208,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4060,10 +4219,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4072,23 +4231,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4112,13 +4267,13 @@
         <v>82</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>82</v>
@@ -4136,19 +4291,19 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4157,13 +4312,13 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4171,10 +4326,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4185,7 +4340,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4194,23 +4349,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4219,7 +4370,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4258,19 +4409,19 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4279,13 +4430,13 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4293,21 +4444,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4316,23 +4467,21 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4380,34 +4529,34 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4415,10 +4564,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4426,33 +4575,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>257</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4461,7 +4612,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -4476,13 +4627,13 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
@@ -4500,34 +4651,34 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4535,21 +4686,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4558,22 +4709,22 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4598,13 +4749,13 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -4622,34 +4773,34 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4657,21 +4808,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4680,22 +4831,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4705,7 +4856,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -4720,13 +4871,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -4744,45 +4895,45 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4793,7 +4944,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4802,20 +4953,18 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>95</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>286</v>
+        <v>183</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4864,19 +5013,19 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -4885,13 +5034,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>291</v>
+        <v>187</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4899,14 +5048,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4922,21 +5071,21 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>293</v>
+        <v>141</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>294</v>
+        <v>142</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4972,19 +5121,19 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4996,22 +5145,22 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5019,10 +5168,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5030,10 +5179,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5042,22 +5191,22 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>304</v>
+        <v>268</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5094,68 +5243,68 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5164,22 +5313,22 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5189,7 +5338,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5228,45 +5377,45 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5274,10 +5423,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5286,22 +5435,22 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>284</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5326,13 +5475,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5350,34 +5499,34 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5385,14 +5534,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5408,23 +5557,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>191</v>
+        <v>294</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5448,13 +5595,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5472,7 +5619,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5484,68 +5631,68 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>342</v>
+        <v>304</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5594,34 +5741,34 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>338</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5629,21 +5776,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5652,21 +5799,23 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5690,13 +5839,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5714,45 +5863,45 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>346</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>354</v>
+        <v>319</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5763,7 +5912,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5772,23 +5921,21 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5812,13 +5959,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5836,34 +5983,34 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5871,10 +6018,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5885,7 +6032,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -5894,21 +6041,21 @@
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5956,45 +6103,45 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>372</v>
+        <v>336</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6002,10 +6149,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6014,21 +6161,23 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6064,68 +6213,68 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>382</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6134,22 +6283,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>384</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>385</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6198,19 +6347,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>389</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6219,24 +6368,24 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>390</v>
+        <v>347</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>391</v>
+        <v>348</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6247,7 +6396,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6259,16 +6408,20 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6292,13 +6445,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6316,19 +6469,19 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6340,10 +6493,10 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6351,14 +6504,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>137</v>
+        <v>364</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6377,18 +6530,20 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>139</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6412,13 +6567,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6436,7 +6591,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6448,7 +6603,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6457,28 +6612,28 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>221</v>
+        <v>372</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6488,28 +6643,28 @@
         <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>138</v>
+        <v>376</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>141</v>
+        <v>379</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>147</v>
+        <v>380</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6558,7 +6713,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6570,7 +6725,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6582,10 +6737,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>135</v>
+        <v>381</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6593,10 +6748,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6607,7 +6762,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6619,15 +6774,17 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>400</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6652,13 +6809,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6676,19 +6833,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6697,24 +6854,24 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6725,7 +6882,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6737,15 +6894,17 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6794,19 +6953,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6815,13 +6974,13 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6829,10 +6988,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6843,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6855,19 +7014,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6892,13 +7051,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>116</v>
+        <v>251</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6916,34 +7075,34 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>406</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -6951,10 +7110,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6965,7 +7124,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6977,20 +7136,18 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7014,13 +7171,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7038,45 +7195,45 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>413</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7087,7 +7244,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7099,18 +7256,18 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7158,45 +7315,45 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7207,7 +7364,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7219,16 +7376,20 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7276,20 +7437,20 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7297,13 +7458,13 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7311,10 +7472,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7325,7 +7486,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7334,20 +7495,18 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7396,19 +7555,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>185</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7417,13 +7576,13 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7431,14 +7590,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7454,19 +7613,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>141</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>142</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>189</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>144</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7516,7 +7675,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>190</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7528,7 +7687,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7537,13 +7696,13 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7551,14 +7710,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7571,25 +7730,25 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>384</v>
+        <v>141</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>450</v>
+        <v>193</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>451</v>
+        <v>194</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>452</v>
+        <v>144</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>453</v>
+        <v>150</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7638,7 +7797,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>449</v>
+        <v>195</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7650,7 +7809,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7659,13 +7818,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7673,10 +7832,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7687,7 +7846,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -7699,13 +7858,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>217</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>218</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>219</v>
+        <v>441</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7756,19 +7915,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -7780,10 +7939,10 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>221</v>
+        <v>433</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7791,21 +7950,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7817,17 +7976,15 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>138</v>
+        <v>439</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>139</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7876,19 +8033,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>227</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7900,10 +8057,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>433</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7911,46 +8068,42 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7974,13 +8127,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7998,19 +8151,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8022,10 +8175,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>135</v>
+        <v>433</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8033,10 +8186,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8044,10 +8197,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8056,22 +8209,22 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>458</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8096,13 +8249,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>208</v>
+        <v>459</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>209</v>
+        <v>460</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8120,34 +8273,34 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>212</v>
+        <v>461</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>213</v>
+        <v>462</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>214</v>
+        <v>373</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8155,10 +8308,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8169,7 +8322,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8178,22 +8331,22 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="M53" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8218,13 +8371,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8242,45 +8395,45 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>311</v>
+        <v>461</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>312</v>
+        <v>462</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8291,7 +8444,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8303,19 +8456,17 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>471</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>320</v>
+        <v>474</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8340,13 +8491,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8364,19 +8515,19 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8385,13 +8536,13 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8399,21 +8550,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8425,20 +8576,16 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>477</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>328</v>
+        <v>478</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8462,13 +8609,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8486,45 +8633,45 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>336</v>
+        <v>433</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8544,23 +8691,21 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8608,7 +8753,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8620,7 +8765,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8629,20 +8774,1232 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>391</v>
+        <v>486</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP56">
+  <autoFilter ref="A1:AP66">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8652,7 +10009,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T08:50:38+00:00</t>
+    <t>2023-05-10T09:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:32+00:00</t>
+    <t>2023-05-10T09:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:16:57+00:00</t>
+    <t>2023-05-10T09:45:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:45:15+00:00</t>
+    <t>2023-05-10T09:50:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T09:50:54+00:00</t>
+    <t>2023-05-10T10:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:15:35+00:00</t>
+    <t>2023-05-10T10:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T10:16:16+00:00</t>
+    <t>2023-05-10T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:21+00:00</t>
+    <t>2023-05-10T11:05:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:05:55+00:00</t>
+    <t>2023-05-10T11:27:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:27:56+00:00</t>
+    <t>2023-05-10T11:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T11:35:39+00:00</t>
+    <t>2023-05-10T12:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:05+00:00</t>
+    <t>2023-05-10T12:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-10T12:21:34+00:00</t>
+    <t>2023-05-11T06:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:48:00+00:00</t>
+    <t>2023-05-11T06:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T06:54:25+00:00</t>
+    <t>2023-05-11T08:35:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:35:45+00:00</t>
+    <t>2023-05-11T08:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T08:41:43+00:00</t>
+    <t>2023-05-11T09:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:08:26+00:00</t>
+    <t>2023-05-11T09:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T09:17:12+00:00</t>
+    <t>2023-05-11T10:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:25+00:00</t>
+    <t>2023-05-11T10:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:17:56+00:00</t>
+    <t>2023-05-11T10:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:34:10+00:00</t>
+    <t>2023-05-11T10:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:41:58+00:00</t>
+    <t>2023-05-11T10:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:16+00:00</t>
+    <t>2023-05-11T10:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T10:56:44+00:00</t>
+    <t>2023-05-11T11:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:14:34+00:00</t>
+    <t>2023-05-11T11:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-patient-is-new</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-patient-is-new</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:21:30+00:00</t>
+    <t>2023-05-11T11:55:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T11:55:17+00:00</t>
+    <t>2023-05-11T12:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv.json/StructureDefinition/hiv-patient-is-new</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-patient-is-new</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:03:20+00:00</t>
+    <t>2023-05-11T12:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:08:48+00:00</t>
+    <t>2023-05-11T12:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:16:35+00:00</t>
+    <t>2023-05-11T12:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:20:22+00:00</t>
+    <t>2023-05-11T12:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T12:21:18+00:00</t>
+    <t>2023-05-11T15:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T15:26:02+00:00</t>
+    <t>2023-05-11T16:43:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:02+00:00</t>
+    <t>2023-05-11T16:43:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:43:55+00:00</t>
+    <t>2023-05-11T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:57:46+00:00</t>
+    <t>2023-05-11T16:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T16:58:30+00:00</t>
+    <t>2023-05-11T17:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:02+00:00</t>
+    <t>2023-05-11T17:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-patient-is-new</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-patient-is-new</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T17:51:30+00:00</t>
+    <t>2023-05-11T18:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:15:51+00:00</t>
+    <t>2023-05-11T18:16:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ImplementationGuide/openhie.fhir.rwanda.hiv/StructureDefinition/hiv-patient-is-new</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/StructureDefinition/hiv-patient-is-new</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:16:31+00:00</t>
+    <t>2023-05-11T18:27:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:27:59+00:00</t>
+    <t>2023-05-11T18:29:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:29:46+00:00</t>
+    <t>2023-05-11T18:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:48:31+00:00</t>
+    <t>2023-05-11T18:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T18:54:41+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:41:30+00:00</t>
+    <t>2023-05-11T19:42:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:42:15+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:23:29+00:00</t>
+    <t>2023-05-11T20:24:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:24:51+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T02:48:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:48:54+00:00</t>
+    <t>2023-05-12T02:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T02:49:37+00:00</t>
+    <t>2023-05-12T07:30:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:25+00:00</t>
+    <t>2023-05-12T07:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:30:35+00:00</t>
+    <t>2023-05-12T07:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:36:30+00:00</t>
+    <t>2023-05-12T07:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:54:06+00:00</t>
+    <t>2023-05-12T07:55:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:55:51+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:26:59+00:00</t>
+    <t>2023-05-12T10:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:27:50+00:00</t>
+    <t>2023-05-12T10:32:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:32:06+00:00</t>
+    <t>2023-05-12T10:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:40:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:37:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:37:18+00:00</t>
+    <t>2023-05-12T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:51:30+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:07:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:07:38+00:00</t>
+    <t>2023-05-23T09:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T09:13:26+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
